--- a/annexes/wealth/wealth_revenue_tables.xlsx
+++ b/annexes/wealth/wealth_revenue_tables.xlsx
@@ -484,25 +484,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>3067</v>
+        <v>3165</v>
       </c>
       <c r="C2" t="n">
-        <v>2725</v>
+        <v>2812</v>
       </c>
       <c r="D2" t="n">
-        <v>3179</v>
+        <v>3281</v>
       </c>
       <c r="E2" t="n">
-        <v>2035</v>
+        <v>2101</v>
       </c>
       <c r="F2" t="n">
-        <v>8971</v>
+        <v>9259</v>
       </c>
       <c r="G2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H2" t="n">
-        <v>5215</v>
+        <v>5382</v>
       </c>
     </row>
     <row r="3">
@@ -510,25 +510,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>1888</v>
+        <v>1949</v>
       </c>
       <c r="C3" t="n">
-        <v>1277</v>
+        <v>1318</v>
       </c>
       <c r="D3" t="n">
-        <v>2345</v>
+        <v>2420</v>
       </c>
       <c r="E3" t="n">
-        <v>2684</v>
+        <v>2770</v>
       </c>
       <c r="F3" t="n">
-        <v>5510</v>
+        <v>5687</v>
       </c>
       <c r="G3" t="n">
         <v>0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>5029</v>
+        <v>5190</v>
       </c>
     </row>
     <row r="4">
@@ -536,25 +536,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1197</v>
+        <v>1235</v>
       </c>
       <c r="C4" t="n">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="D4" t="n">
-        <v>1121</v>
+        <v>1157</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2793</v>
+        <v>2882</v>
       </c>
       <c r="G4" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H4" t="n">
-        <v>1121</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="5">
@@ -562,25 +562,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>846</v>
+        <v>874</v>
       </c>
       <c r="C5" t="n">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="D5" t="n">
-        <v>596</v>
+        <v>616</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1888</v>
+        <v>1948</v>
       </c>
       <c r="G5" t="n">
         <v>0.13</v>
       </c>
       <c r="H5" t="n">
-        <v>596</v>
+        <v>616</v>
       </c>
     </row>
     <row r="6">
@@ -588,25 +588,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C6" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D6" t="n">
-        <v>525</v>
+        <v>542</v>
       </c>
       <c r="E6" t="n">
-        <v>1077</v>
+        <v>1111</v>
       </c>
       <c r="F6" t="n">
-        <v>1015</v>
+        <v>1047</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H6" t="n">
-        <v>1602</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="7">
@@ -614,25 +614,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="C7" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D7" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>908</v>
+        <v>937</v>
       </c>
       <c r="G7" t="n">
-        <v>0.088</v>
+        <v>0.091</v>
       </c>
       <c r="H7" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8">
@@ -640,25 +640,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C8" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="E8" t="n">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="F8" t="n">
-        <v>895</v>
+        <v>923</v>
       </c>
       <c r="G8" t="n">
         <v>0.19</v>
       </c>
       <c r="H8" t="n">
-        <v>618</v>
+        <v>638</v>
       </c>
     </row>
     <row r="9">
@@ -666,25 +666,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C9" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>798</v>
+        <v>824</v>
       </c>
       <c r="G9" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H9" t="n">
-        <v>315</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -692,25 +692,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="C10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -718,25 +718,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="E11" t="n">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F11" t="n">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="G11" t="n">
         <v>0.15</v>
       </c>
       <c r="H11" t="n">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="12">
@@ -744,25 +744,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="G12" t="n">
-        <v>0.081</v>
+        <v>0.084</v>
       </c>
       <c r="H12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -770,25 +770,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="G13" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H13" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
@@ -796,25 +796,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C14" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="G14" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H14" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -822,25 +822,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E15" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="F15" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="G15" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H15" t="n">
-        <v>406</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16">
@@ -848,25 +848,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G16" t="n">
-        <v>0.098</v>
+        <v>0.1</v>
       </c>
       <c r="H16" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
@@ -874,25 +874,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G17" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="H17" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -900,25 +900,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G18" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="H18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -926,25 +926,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G19" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="H19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -958,19 +958,19 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
       </c>
       <c r="H20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -984,19 +984,19 @@
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
         <v>0.14</v>
       </c>
       <c r="H21" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
@@ -1004,25 +1004,25 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C22" t="n">
         <v>14</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G22" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="H22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -1030,25 +1030,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="n">
         <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -1056,7 +1056,7 @@
         <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24" t="n">
         <v>10</v>
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G24" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="H24" t="n">
         <v>7</v>
@@ -1085,7 +1085,7 @@
         <v>14</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -1094,10 +1094,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.073</v>
+        <v>0.076</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
@@ -1123,7 +1123,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
@@ -1149,7 +1149,7 @@
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
         <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1186,25 +1186,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>10188</v>
+        <v>10515</v>
       </c>
       <c r="C29" t="n">
-        <v>6331</v>
+        <v>6534</v>
       </c>
       <c r="D29" t="n">
-        <v>9591</v>
+        <v>9900</v>
       </c>
       <c r="E29" t="n">
-        <v>6553</v>
+        <v>6764</v>
       </c>
       <c r="F29" t="n">
-        <v>26100</v>
+        <v>26900</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1531</v>
+        <v>0.158</v>
       </c>
       <c r="H29" t="n">
-        <v>16144</v>
+        <v>16663</v>
       </c>
     </row>
   </sheetData>
@@ -1249,25 +1249,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>3067</v>
+        <v>3165</v>
       </c>
       <c r="C2" t="n">
-        <v>2725</v>
+        <v>2812</v>
       </c>
       <c r="D2" t="n">
-        <v>3291</v>
+        <v>3397</v>
       </c>
       <c r="E2" t="n">
-        <v>8494</v>
+        <v>8767</v>
       </c>
       <c r="F2" t="n">
-        <v>9083</v>
+        <v>9375</v>
       </c>
       <c r="G2" t="n">
         <v>0.22</v>
       </c>
       <c r="H2" t="n">
-        <v>11785</v>
+        <v>12164</v>
       </c>
     </row>
     <row r="3">
@@ -1275,25 +1275,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>1888</v>
+        <v>1949</v>
       </c>
       <c r="C3" t="n">
-        <v>1277</v>
+        <v>1318</v>
       </c>
       <c r="D3" t="n">
-        <v>3771</v>
+        <v>3893</v>
       </c>
       <c r="E3" t="n">
-        <v>9733</v>
+        <v>10046</v>
       </c>
       <c r="F3" t="n">
-        <v>6936</v>
+        <v>7159</v>
       </c>
       <c r="G3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H3" t="n">
-        <v>13504</v>
+        <v>13938</v>
       </c>
     </row>
     <row r="4">
@@ -1301,25 +1301,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1197</v>
+        <v>1235</v>
       </c>
       <c r="C4" t="n">
-        <v>475</v>
+        <v>490</v>
       </c>
       <c r="D4" t="n">
-        <v>1622</v>
+        <v>1674</v>
       </c>
       <c r="E4" t="n">
-        <v>4186</v>
+        <v>4321</v>
       </c>
       <c r="F4" t="n">
-        <v>3294</v>
+        <v>3400</v>
       </c>
       <c r="G4" t="n">
         <v>0.16</v>
       </c>
       <c r="H4" t="n">
-        <v>5808</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="5">
@@ -1327,25 +1327,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>846</v>
+        <v>874</v>
       </c>
       <c r="C5" t="n">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="D5" t="n">
-        <v>1007</v>
+        <v>1040</v>
       </c>
       <c r="E5" t="n">
-        <v>2600</v>
+        <v>2683</v>
       </c>
       <c r="F5" t="n">
-        <v>2299</v>
+        <v>2372</v>
       </c>
       <c r="G5" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3607</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="6">
@@ -1353,25 +1353,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C6" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D6" t="n">
-        <v>899</v>
+        <v>928</v>
       </c>
       <c r="E6" t="n">
-        <v>2320</v>
+        <v>2394</v>
       </c>
       <c r="F6" t="n">
-        <v>1389</v>
+        <v>1433</v>
       </c>
       <c r="G6" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H6" t="n">
-        <v>3219</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="7">
@@ -1379,25 +1379,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>648</v>
+        <v>669</v>
       </c>
       <c r="C7" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D7" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E7" t="n">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="F7" t="n">
-        <v>954</v>
+        <v>985</v>
       </c>
       <c r="G7" t="n">
-        <v>0.092</v>
+        <v>0.095</v>
       </c>
       <c r="H7" t="n">
-        <v>666</v>
+        <v>688</v>
       </c>
     </row>
     <row r="8">
@@ -1405,25 +1405,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C8" t="n">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="E8" t="n">
-        <v>960</v>
+        <v>991</v>
       </c>
       <c r="F8" t="n">
-        <v>938</v>
+        <v>968</v>
       </c>
       <c r="G8" t="n">
         <v>0.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1333</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="9">
@@ -1431,25 +1431,25 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D9" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E9" t="n">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="F9" t="n">
-        <v>767</v>
+        <v>791</v>
       </c>
       <c r="G9" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H9" t="n">
-        <v>703</v>
+        <v>726</v>
       </c>
     </row>
     <row r="10">
@@ -1457,25 +1457,25 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C10" t="n">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E10" t="n">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="F10" t="n">
-        <v>628</v>
+        <v>648</v>
       </c>
       <c r="G10" t="n">
-        <v>0.088</v>
+        <v>0.091</v>
       </c>
       <c r="H10" t="n">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="11">
@@ -1483,25 +1483,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E11" t="n">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="F11" t="n">
-        <v>586</v>
+        <v>604</v>
       </c>
       <c r="G11" t="n">
         <v>0.16</v>
       </c>
       <c r="H11" t="n">
-        <v>888</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12">
@@ -1509,25 +1509,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="n">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="E12" t="n">
-        <v>720</v>
+        <v>743</v>
       </c>
       <c r="F12" t="n">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="G12" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H12" t="n">
-        <v>998</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="13">
@@ -1535,25 +1535,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C13" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="E13" t="n">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="F13" t="n">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="G13" t="n">
         <v>0.15</v>
       </c>
       <c r="H13" t="n">
-        <v>1185</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="14">
@@ -1561,25 +1561,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C14" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" t="n">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="G14" t="n">
         <v>0.13</v>
       </c>
       <c r="H14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -1587,25 +1587,25 @@
         <v>24</v>
       </c>
       <c r="B15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E15" t="n">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="F15" t="n">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G15" t="n">
         <v>0.13</v>
       </c>
       <c r="H15" t="n">
-        <v>721</v>
+        <v>744</v>
       </c>
     </row>
     <row r="16">
@@ -1619,19 +1619,19 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E16" t="n">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="F16" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G16" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="H16" t="n">
-        <v>833</v>
+        <v>860</v>
       </c>
     </row>
     <row r="17">
@@ -1639,25 +1639,25 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C17" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F17" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G17" t="n">
-        <v>0.083</v>
+        <v>0.086</v>
       </c>
       <c r="H17" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18">
@@ -1665,25 +1665,25 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C18" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E18" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F18" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G18" t="n">
-        <v>0.048</v>
+        <v>0.049</v>
       </c>
       <c r="H18" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="19">
@@ -1691,25 +1691,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E19" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F19" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G19" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
       <c r="H19" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20">
@@ -1717,25 +1717,25 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
         <v>14</v>
       </c>
       <c r="F20" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G20" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1743,25 +1743,25 @@
         <v>28</v>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
         <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G21" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
       <c r="H21" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22">
@@ -1769,25 +1769,25 @@
         <v>29</v>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
         <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>27</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
       <c r="H22" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -1798,22 +1798,22 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
         <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
       </c>
       <c r="H23" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
@@ -1833,10 +1833,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1856,16 +1856,16 @@
         <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="H25" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
@@ -1873,7 +1873,7 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C26" t="n">
         <v>10</v>
@@ -1885,10 +1885,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1914,7 +1914,7 @@
         <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1925,7 +1925,7 @@
         <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1940,7 +1940,7 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1951,25 +1951,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>10188</v>
+        <v>10515</v>
       </c>
       <c r="C29" t="n">
-        <v>6331</v>
+        <v>6534</v>
       </c>
       <c r="D29" t="n">
-        <v>13073</v>
+        <v>13493</v>
       </c>
       <c r="E29" t="n">
-        <v>33736</v>
+        <v>34820</v>
       </c>
       <c r="F29" t="n">
-        <v>29600</v>
+        <v>30500</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1735</v>
+        <v>0.1791</v>
       </c>
       <c r="H29" t="n">
-        <v>46808</v>
+        <v>48313</v>
       </c>
     </row>
   </sheetData>
@@ -2014,25 +2014,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>2955</v>
+        <v>3050</v>
       </c>
       <c r="C2" t="n">
-        <v>2618</v>
+        <v>2702</v>
       </c>
       <c r="D2" t="n">
-        <v>2511</v>
+        <v>2592</v>
       </c>
       <c r="E2" t="n">
-        <v>4809</v>
+        <v>4963</v>
       </c>
       <c r="F2" t="n">
-        <v>8084</v>
+        <v>8344</v>
       </c>
       <c r="G2" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>7320</v>
+        <v>7556</v>
       </c>
     </row>
     <row r="3">
@@ -2040,25 +2040,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>1932</v>
+        <v>1994</v>
       </c>
       <c r="C3" t="n">
-        <v>1335</v>
+        <v>1378</v>
       </c>
       <c r="D3" t="n">
-        <v>3195</v>
+        <v>3298</v>
       </c>
       <c r="E3" t="n">
-        <v>8537</v>
+        <v>8812</v>
       </c>
       <c r="F3" t="n">
-        <v>6462</v>
+        <v>6670</v>
       </c>
       <c r="G3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H3" t="n">
-        <v>11732</v>
+        <v>12109</v>
       </c>
     </row>
     <row r="4">
@@ -2066,25 +2066,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1140</v>
+        <v>1177</v>
       </c>
       <c r="C4" t="n">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="D4" t="n">
-        <v>963</v>
+        <v>994</v>
       </c>
       <c r="E4" t="n">
-        <v>1286</v>
+        <v>1327</v>
       </c>
       <c r="F4" t="n">
-        <v>2537</v>
+        <v>2618</v>
       </c>
       <c r="G4" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H4" t="n">
-        <v>2249</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="5">
@@ -2092,25 +2092,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>825</v>
+        <v>851</v>
       </c>
       <c r="C5" t="n">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D5" t="n">
-        <v>839</v>
+        <v>866</v>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>1409</v>
       </c>
       <c r="F5" t="n">
-        <v>2084</v>
+        <v>2151</v>
       </c>
       <c r="G5" t="n">
         <v>0.14</v>
       </c>
       <c r="H5" t="n">
-        <v>2204</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="6">
@@ -2118,25 +2118,25 @@
         <v>14</v>
       </c>
       <c r="B6" t="n">
+        <v>296</v>
+      </c>
+      <c r="C6" t="n">
         <v>287</v>
       </c>
-      <c r="C6" t="n">
-        <v>278</v>
-      </c>
       <c r="D6" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="E6" t="n">
-        <v>814</v>
+        <v>841</v>
       </c>
       <c r="F6" t="n">
-        <v>891</v>
+        <v>920</v>
       </c>
       <c r="G6" t="n">
         <v>0.19</v>
       </c>
       <c r="H6" t="n">
-        <v>1141</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="7">
@@ -2144,25 +2144,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="C7" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D7" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E7" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F7" t="n">
-        <v>885</v>
+        <v>913</v>
       </c>
       <c r="G7" t="n">
-        <v>0.086</v>
+        <v>0.088</v>
       </c>
       <c r="H7" t="n">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8">
@@ -2170,25 +2170,25 @@
         <v>16</v>
       </c>
       <c r="B8" t="n">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E8" t="n">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="F8" t="n">
-        <v>700</v>
+        <v>722</v>
       </c>
       <c r="G8" t="n">
         <v>0.12</v>
       </c>
       <c r="H8" t="n">
-        <v>691</v>
+        <v>713</v>
       </c>
     </row>
     <row r="9">
@@ -2196,25 +2196,25 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C9" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="E9" t="n">
-        <v>803</v>
+        <v>829</v>
       </c>
       <c r="F9" t="n">
-        <v>690</v>
+        <v>712</v>
       </c>
       <c r="G9" t="n">
         <v>0.14</v>
       </c>
       <c r="H9" t="n">
-        <v>1105</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="10">
@@ -2222,25 +2222,25 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E10" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F10" t="n">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="G10" t="n">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="H10" t="n">
-        <v>354</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11">
@@ -2248,25 +2248,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E11" t="n">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="F11" t="n">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="G11" t="n">
         <v>0.14</v>
       </c>
       <c r="H11" t="n">
-        <v>610</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12">
@@ -2274,25 +2274,25 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E12" t="n">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="F12" t="n">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="G12" t="n">
         <v>0.11</v>
       </c>
       <c r="H12" t="n">
-        <v>697</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13">
@@ -2300,25 +2300,25 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C13" t="n">
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="G13" t="n">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="H13" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -2326,25 +2326,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C14" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="G14" t="n">
         <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -2352,25 +2352,25 @@
         <v>22</v>
       </c>
       <c r="B15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="G15" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16">
@@ -2378,25 +2378,25 @@
         <v>25</v>
       </c>
       <c r="B16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E16" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F16" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G16" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="H16" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17">
@@ -2404,25 +2404,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E17" t="n">
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G17" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="H17" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18">
@@ -2430,25 +2430,25 @@
         <v>35</v>
       </c>
       <c r="B18" t="n">
-        <v>9436</v>
+        <v>9739</v>
       </c>
       <c r="C18" t="n">
-        <v>5960</v>
+        <v>6151</v>
       </c>
       <c r="D18" t="n">
-        <v>9440</v>
+        <v>9744</v>
       </c>
       <c r="E18" t="n">
-        <v>19591</v>
+        <v>20220</v>
       </c>
       <c r="F18" t="n">
-        <v>24800</v>
+        <v>25600</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1456</v>
+        <v>0.1503</v>
       </c>
       <c r="H18" t="n">
-        <v>29031</v>
+        <v>29964</v>
       </c>
     </row>
   </sheetData>
@@ -2493,25 +2493,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>2955</v>
+        <v>3050</v>
       </c>
       <c r="C2" t="n">
-        <v>2618</v>
+        <v>2702</v>
       </c>
       <c r="D2" t="n">
-        <v>3291</v>
+        <v>3397</v>
       </c>
       <c r="E2" t="n">
-        <v>8494</v>
+        <v>8767</v>
       </c>
       <c r="F2" t="n">
-        <v>8864</v>
+        <v>9149</v>
       </c>
       <c r="G2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H2" t="n">
-        <v>11785</v>
+        <v>12164</v>
       </c>
     </row>
     <row r="3">
@@ -2519,25 +2519,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>1932</v>
+        <v>1994</v>
       </c>
       <c r="C3" t="n">
-        <v>1335</v>
+        <v>1378</v>
       </c>
       <c r="D3" t="n">
-        <v>3771</v>
+        <v>3893</v>
       </c>
       <c r="E3" t="n">
-        <v>9733</v>
+        <v>10046</v>
       </c>
       <c r="F3" t="n">
-        <v>7038</v>
+        <v>7265</v>
       </c>
       <c r="G3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H3" t="n">
-        <v>13504</v>
+        <v>13938</v>
       </c>
     </row>
     <row r="4">
@@ -2545,25 +2545,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1140</v>
+        <v>1177</v>
       </c>
       <c r="C4" t="n">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="D4" t="n">
-        <v>1622</v>
+        <v>1674</v>
       </c>
       <c r="E4" t="n">
-        <v>4186</v>
+        <v>4321</v>
       </c>
       <c r="F4" t="n">
-        <v>3196</v>
+        <v>3299</v>
       </c>
       <c r="G4" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H4" t="n">
-        <v>5808</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="5">
@@ -2571,25 +2571,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>825</v>
+        <v>851</v>
       </c>
       <c r="C5" t="n">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D5" t="n">
-        <v>1007</v>
+        <v>1040</v>
       </c>
       <c r="E5" t="n">
-        <v>2600</v>
+        <v>2683</v>
       </c>
       <c r="F5" t="n">
-        <v>2252</v>
+        <v>2325</v>
       </c>
       <c r="G5" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3607</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="6">
@@ -2597,25 +2597,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D6" t="n">
-        <v>899</v>
+        <v>928</v>
       </c>
       <c r="E6" t="n">
-        <v>2320</v>
+        <v>2394</v>
       </c>
       <c r="F6" t="n">
-        <v>1286</v>
+        <v>1328</v>
       </c>
       <c r="G6" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3219</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="7">
@@ -2623,25 +2623,25 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
+        <v>296</v>
+      </c>
+      <c r="C7" t="n">
         <v>287</v>
       </c>
-      <c r="C7" t="n">
-        <v>278</v>
-      </c>
       <c r="D7" t="n">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="E7" t="n">
-        <v>960</v>
+        <v>991</v>
       </c>
       <c r="F7" t="n">
-        <v>937</v>
+        <v>967</v>
       </c>
       <c r="G7" t="n">
         <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1333</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="8">
@@ -2649,25 +2649,25 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="C8" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D8" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E8" t="n">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="F8" t="n">
-        <v>858</v>
+        <v>886</v>
       </c>
       <c r="G8" t="n">
-        <v>0.083</v>
+        <v>0.086</v>
       </c>
       <c r="H8" t="n">
-        <v>666</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9">
@@ -2675,25 +2675,25 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E9" t="n">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="F9" t="n">
-        <v>716</v>
+        <v>739</v>
       </c>
       <c r="G9" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H9" t="n">
-        <v>703</v>
+        <v>726</v>
       </c>
     </row>
     <row r="10">
@@ -2701,25 +2701,25 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C10" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E10" t="n">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="F10" t="n">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="G10" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H10" t="n">
-        <v>888</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11">
@@ -2727,25 +2727,25 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C11" t="n">
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="E11" t="n">
-        <v>720</v>
+        <v>743</v>
       </c>
       <c r="F11" t="n">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H11" t="n">
-        <v>998</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="12">
@@ -2753,25 +2753,25 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C12" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E12" t="n">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="F12" t="n">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07</v>
+        <v>0.072</v>
       </c>
       <c r="H12" t="n">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13">
@@ -2779,25 +2779,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="E13" t="n">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="F13" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="G13" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H13" t="n">
-        <v>1185</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="14">
@@ -2805,25 +2805,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C14" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" t="n">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="G14" t="n">
         <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -2831,25 +2831,25 @@
         <v>22</v>
       </c>
       <c r="B15" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E15" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F15" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G15" t="n">
-        <v>0.078</v>
+        <v>0.08</v>
       </c>
       <c r="H15" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16">
@@ -2857,25 +2857,25 @@
         <v>25</v>
       </c>
       <c r="B16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E16" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F16" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G16" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="H16" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17">
@@ -2883,25 +2883,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E17" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F17" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G17" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="H17" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18">
@@ -2909,25 +2909,25 @@
         <v>35</v>
       </c>
       <c r="B18" t="n">
-        <v>9436</v>
+        <v>9739</v>
       </c>
       <c r="C18" t="n">
-        <v>5960</v>
+        <v>6151</v>
       </c>
       <c r="D18" t="n">
-        <v>12565</v>
+        <v>12969</v>
       </c>
       <c r="E18" t="n">
-        <v>32427</v>
+        <v>33469</v>
       </c>
       <c r="F18" t="n">
-        <v>28000</v>
+        <v>28900</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1639</v>
+        <v>0.1692</v>
       </c>
       <c r="H18" t="n">
-        <v>44992</v>
+        <v>46438</v>
       </c>
     </row>
   </sheetData>
@@ -2972,25 +2972,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>2955</v>
+        <v>3050</v>
       </c>
       <c r="C2" t="n">
-        <v>2618</v>
+        <v>2702</v>
       </c>
       <c r="D2" t="n">
-        <v>2511</v>
+        <v>2592</v>
       </c>
       <c r="E2" t="n">
-        <v>4809</v>
+        <v>4963</v>
       </c>
       <c r="F2" t="n">
-        <v>8084</v>
+        <v>8344</v>
       </c>
       <c r="G2" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>7320</v>
+        <v>7556</v>
       </c>
     </row>
     <row r="3">
@@ -2998,25 +2998,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>1932</v>
+        <v>1994</v>
       </c>
       <c r="C3" t="n">
-        <v>1335</v>
+        <v>1378</v>
       </c>
       <c r="D3" t="n">
-        <v>3195</v>
+        <v>3298</v>
       </c>
       <c r="E3" t="n">
-        <v>8537</v>
+        <v>8812</v>
       </c>
       <c r="F3" t="n">
-        <v>6462</v>
+        <v>6670</v>
       </c>
       <c r="G3" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H3" t="n">
-        <v>11732</v>
+        <v>12109</v>
       </c>
     </row>
     <row r="4">
@@ -3024,25 +3024,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1140</v>
+        <v>1177</v>
       </c>
       <c r="C4" t="n">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="D4" t="n">
-        <v>963</v>
+        <v>994</v>
       </c>
       <c r="E4" t="n">
-        <v>1286</v>
+        <v>1327</v>
       </c>
       <c r="F4" t="n">
-        <v>2537</v>
+        <v>2618</v>
       </c>
       <c r="G4" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H4" t="n">
-        <v>2249</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="5">
@@ -3050,25 +3050,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>825</v>
+        <v>851</v>
       </c>
       <c r="C5" t="n">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D5" t="n">
-        <v>839</v>
+        <v>866</v>
       </c>
       <c r="E5" t="n">
-        <v>1365</v>
+        <v>1409</v>
       </c>
       <c r="F5" t="n">
-        <v>2084</v>
+        <v>2151</v>
       </c>
       <c r="G5" t="n">
         <v>0.14</v>
       </c>
       <c r="H5" t="n">
-        <v>2204</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="6">
@@ -3076,25 +3076,25 @@
         <v>14</v>
       </c>
       <c r="B6" t="n">
+        <v>296</v>
+      </c>
+      <c r="C6" t="n">
         <v>287</v>
       </c>
-      <c r="C6" t="n">
-        <v>278</v>
-      </c>
       <c r="D6" t="n">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="E6" t="n">
-        <v>814</v>
+        <v>841</v>
       </c>
       <c r="F6" t="n">
-        <v>891</v>
+        <v>920</v>
       </c>
       <c r="G6" t="n">
         <v>0.19</v>
       </c>
       <c r="H6" t="n">
-        <v>1141</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="7">
@@ -3102,25 +3102,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="C7" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D7" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="E7" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F7" t="n">
-        <v>885</v>
+        <v>913</v>
       </c>
       <c r="G7" t="n">
-        <v>0.086</v>
+        <v>0.088</v>
       </c>
       <c r="H7" t="n">
-        <v>390</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8">
@@ -3128,25 +3128,25 @@
         <v>16</v>
       </c>
       <c r="B8" t="n">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="C8" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E8" t="n">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="F8" t="n">
-        <v>700</v>
+        <v>722</v>
       </c>
       <c r="G8" t="n">
         <v>0.12</v>
       </c>
       <c r="H8" t="n">
-        <v>691</v>
+        <v>713</v>
       </c>
     </row>
     <row r="9">
@@ -3154,25 +3154,25 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C9" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="E9" t="n">
-        <v>803</v>
+        <v>829</v>
       </c>
       <c r="F9" t="n">
-        <v>690</v>
+        <v>712</v>
       </c>
       <c r="G9" t="n">
         <v>0.14</v>
       </c>
       <c r="H9" t="n">
-        <v>1105</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="10">
@@ -3180,25 +3180,25 @@
         <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="E10" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F10" t="n">
-        <v>543</v>
+        <v>560</v>
       </c>
       <c r="G10" t="n">
-        <v>0.076</v>
+        <v>0.079</v>
       </c>
       <c r="H10" t="n">
-        <v>354</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11">
@@ -3206,25 +3206,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C11" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E11" t="n">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="F11" t="n">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="G11" t="n">
         <v>0.14</v>
       </c>
       <c r="H11" t="n">
-        <v>610</v>
+        <v>630</v>
       </c>
     </row>
     <row r="12">
@@ -3232,25 +3232,25 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D12" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E12" t="n">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="F12" t="n">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="G12" t="n">
         <v>0.11</v>
       </c>
       <c r="H12" t="n">
-        <v>697</v>
+        <v>719</v>
       </c>
     </row>
     <row r="13">
@@ -3258,25 +3258,25 @@
         <v>18</v>
       </c>
       <c r="B13" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C13" t="n">
         <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E13" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="G13" t="n">
-        <v>0.063</v>
+        <v>0.065</v>
       </c>
       <c r="H13" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14">
@@ -3284,25 +3284,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C14" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="G14" t="n">
         <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15">
@@ -3310,25 +3310,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E15" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="F15" t="n">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="G15" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H15" t="n">
-        <v>406</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16">
@@ -3336,25 +3336,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C16" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E16" t="n">
         <v>8</v>
       </c>
       <c r="F16" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="G16" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="H16" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -3362,25 +3362,25 @@
         <v>25</v>
       </c>
       <c r="B17" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E17" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F17" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="G17" t="n">
-        <v>0.053</v>
+        <v>0.055</v>
       </c>
       <c r="H17" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18">
@@ -3388,25 +3388,25 @@
         <v>23</v>
       </c>
       <c r="B18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
         <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G18" t="n">
-        <v>0.034</v>
+        <v>0.035</v>
       </c>
       <c r="H18" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -3414,25 +3414,25 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="G19" t="n">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="H19" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -3446,19 +3446,19 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G20" t="n">
         <v>0.11</v>
       </c>
       <c r="H20" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -3472,19 +3472,19 @@
         <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
         <v>0.14</v>
       </c>
       <c r="H21" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
@@ -3492,25 +3492,25 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C22" t="n">
         <v>14</v>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G22" t="n">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="H22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -3518,25 +3518,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C23" t="n">
         <v>12</v>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G23" t="n">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -3544,7 +3544,7 @@
         <v>30</v>
       </c>
       <c r="B24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C24" t="n">
         <v>10</v>
@@ -3556,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G24" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="H24" t="n">
         <v>7</v>
@@ -3573,7 +3573,7 @@
         <v>14</v>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" t="n">
         <v>6</v>
@@ -3582,10 +3582,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.073</v>
+        <v>0.076</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
@@ -3611,7 +3611,7 @@
         <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="H26" t="n">
         <v>3</v>
@@ -3637,7 +3637,7 @@
         <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -3663,7 +3663,7 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -3674,25 +3674,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>9667</v>
+        <v>9978</v>
       </c>
       <c r="C29" t="n">
-        <v>6091</v>
+        <v>6287</v>
       </c>
       <c r="D29" t="n">
-        <v>9688</v>
+        <v>10000</v>
       </c>
       <c r="E29" t="n">
-        <v>19886</v>
+        <v>20525</v>
       </c>
       <c r="F29" t="n">
-        <v>25400</v>
+        <v>26300</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1492</v>
+        <v>0.154</v>
       </c>
       <c r="H29" t="n">
-        <v>29574</v>
+        <v>30525</v>
       </c>
     </row>
   </sheetData>
@@ -3737,25 +3737,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>2955</v>
+        <v>3050</v>
       </c>
       <c r="C2" t="n">
-        <v>2618</v>
+        <v>2702</v>
       </c>
       <c r="D2" t="n">
-        <v>3291</v>
+        <v>3397</v>
       </c>
       <c r="E2" t="n">
-        <v>8494</v>
+        <v>8767</v>
       </c>
       <c r="F2" t="n">
-        <v>8864</v>
+        <v>9149</v>
       </c>
       <c r="G2" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="H2" t="n">
-        <v>11785</v>
+        <v>12164</v>
       </c>
     </row>
     <row r="3">
@@ -3763,25 +3763,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>1932</v>
+        <v>1994</v>
       </c>
       <c r="C3" t="n">
-        <v>1335</v>
+        <v>1378</v>
       </c>
       <c r="D3" t="n">
-        <v>3771</v>
+        <v>3893</v>
       </c>
       <c r="E3" t="n">
-        <v>9733</v>
+        <v>10046</v>
       </c>
       <c r="F3" t="n">
-        <v>7038</v>
+        <v>7265</v>
       </c>
       <c r="G3" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H3" t="n">
-        <v>13504</v>
+        <v>13938</v>
       </c>
     </row>
     <row r="4">
@@ -3789,25 +3789,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1140</v>
+        <v>1177</v>
       </c>
       <c r="C4" t="n">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="D4" t="n">
-        <v>1622</v>
+        <v>1674</v>
       </c>
       <c r="E4" t="n">
-        <v>4186</v>
+        <v>4321</v>
       </c>
       <c r="F4" t="n">
-        <v>3196</v>
+        <v>3299</v>
       </c>
       <c r="G4" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H4" t="n">
-        <v>5808</v>
+        <v>5995</v>
       </c>
     </row>
     <row r="5">
@@ -3815,25 +3815,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>825</v>
+        <v>851</v>
       </c>
       <c r="C5" t="n">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D5" t="n">
-        <v>1007</v>
+        <v>1040</v>
       </c>
       <c r="E5" t="n">
-        <v>2600</v>
+        <v>2683</v>
       </c>
       <c r="F5" t="n">
-        <v>2252</v>
+        <v>2325</v>
       </c>
       <c r="G5" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3607</v>
+        <v>3723</v>
       </c>
     </row>
     <row r="6">
@@ -3841,25 +3841,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="C6" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D6" t="n">
-        <v>899</v>
+        <v>928</v>
       </c>
       <c r="E6" t="n">
-        <v>2320</v>
+        <v>2394</v>
       </c>
       <c r="F6" t="n">
-        <v>1286</v>
+        <v>1328</v>
       </c>
       <c r="G6" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3219</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="7">
@@ -3867,25 +3867,25 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
+        <v>296</v>
+      </c>
+      <c r="C7" t="n">
         <v>287</v>
       </c>
-      <c r="C7" t="n">
-        <v>278</v>
-      </c>
       <c r="D7" t="n">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="E7" t="n">
-        <v>960</v>
+        <v>991</v>
       </c>
       <c r="F7" t="n">
-        <v>937</v>
+        <v>967</v>
       </c>
       <c r="G7" t="n">
         <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1333</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="8">
@@ -3893,25 +3893,25 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="C8" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D8" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E8" t="n">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="F8" t="n">
-        <v>858</v>
+        <v>886</v>
       </c>
       <c r="G8" t="n">
-        <v>0.083</v>
+        <v>0.086</v>
       </c>
       <c r="H8" t="n">
-        <v>666</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9">
@@ -3919,25 +3919,25 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="E9" t="n">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="F9" t="n">
-        <v>716</v>
+        <v>739</v>
       </c>
       <c r="G9" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H9" t="n">
-        <v>703</v>
+        <v>726</v>
       </c>
     </row>
     <row r="10">
@@ -3945,25 +3945,25 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C10" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D10" t="n">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="E10" t="n">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="F10" t="n">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="G10" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H10" t="n">
-        <v>888</v>
+        <v>916</v>
       </c>
     </row>
     <row r="11">
@@ -3971,25 +3971,25 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C11" t="n">
         <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="E11" t="n">
-        <v>720</v>
+        <v>743</v>
       </c>
       <c r="F11" t="n">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H11" t="n">
-        <v>998</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="12">
@@ -3997,25 +3997,25 @@
         <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C12" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E12" t="n">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="F12" t="n">
-        <v>498</v>
+        <v>514</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07</v>
+        <v>0.072</v>
       </c>
       <c r="H12" t="n">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13">
@@ -4023,25 +4023,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="E13" t="n">
-        <v>854</v>
+        <v>881</v>
       </c>
       <c r="F13" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="G13" t="n">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="H13" t="n">
-        <v>1185</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="14">
@@ -4049,25 +4049,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C14" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F14" t="n">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="G14" t="n">
         <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -4075,25 +4075,25 @@
         <v>24</v>
       </c>
       <c r="B15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D15" t="n">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="E15" t="n">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="F15" t="n">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G15" t="n">
         <v>0.13</v>
       </c>
       <c r="H15" t="n">
-        <v>721</v>
+        <v>744</v>
       </c>
     </row>
     <row r="16">
@@ -4107,19 +4107,19 @@
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="E16" t="n">
-        <v>601</v>
+        <v>620</v>
       </c>
       <c r="F16" t="n">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G16" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="H16" t="n">
-        <v>833</v>
+        <v>860</v>
       </c>
     </row>
     <row r="17">
@@ -4127,25 +4127,25 @@
         <v>22</v>
       </c>
       <c r="B17" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C17" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F17" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G17" t="n">
-        <v>0.078</v>
+        <v>0.08</v>
       </c>
       <c r="H17" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18">
@@ -4153,25 +4153,25 @@
         <v>25</v>
       </c>
       <c r="B18" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C18" t="n">
         <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E18" t="n">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F18" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G18" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="H18" t="n">
-        <v>278</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19">
@@ -4179,25 +4179,25 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E19" t="n">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F19" t="n">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G19" t="n">
-        <v>0.039</v>
+        <v>0.04</v>
       </c>
       <c r="H19" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20">
@@ -4205,25 +4205,25 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
         <v>14</v>
       </c>
       <c r="F20" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G20" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -4231,25 +4231,25 @@
         <v>28</v>
       </c>
       <c r="B21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
         <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G21" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
       <c r="H21" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22">
@@ -4257,25 +4257,25 @@
         <v>29</v>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" t="n">
         <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E22" t="n">
         <v>27</v>
       </c>
       <c r="F22" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G22" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
       <c r="H22" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
@@ -4286,22 +4286,22 @@
         <v>14</v>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" t="n">
         <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G23" t="n">
         <v>0.1</v>
       </c>
       <c r="H23" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24">
@@ -4321,10 +4321,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G24" t="n">
-        <v>0.052</v>
+        <v>0.054</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -4344,16 +4344,16 @@
         <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
-        <v>0.028</v>
+        <v>0.029</v>
       </c>
       <c r="H25" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26">
@@ -4361,7 +4361,7 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C26" t="n">
         <v>10</v>
@@ -4373,10 +4373,10 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -4413,7 +4413,7 @@
         <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.041</v>
+        <v>0.042</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -4439,25 +4439,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>9667</v>
+        <v>9978</v>
       </c>
       <c r="C29" t="n">
-        <v>6091</v>
+        <v>6287</v>
       </c>
       <c r="D29" t="n">
-        <v>13073</v>
+        <v>13493</v>
       </c>
       <c r="E29" t="n">
-        <v>33736</v>
+        <v>34820</v>
       </c>
       <c r="F29" t="n">
-        <v>28800</v>
+        <v>29800</v>
       </c>
       <c r="G29" t="n">
-        <v>0.169</v>
+        <v>0.1744</v>
       </c>
       <c r="H29" t="n">
-        <v>46808</v>
+        <v>48313</v>
       </c>
     </row>
   </sheetData>

--- a/annexes/wealth/wealth_revenue_tables.xlsx
+++ b/annexes/wealth/wealth_revenue_tables.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Central %GDP</t>
   </si>
   <si>
-    <t xml:space="preserve">Top (c+d)</t>
+    <t xml:space="preserve">Top (c+0.75d)</t>
   </si>
   <si>
     <t xml:space="preserve">Germany</t>
@@ -502,7 +502,7 @@
         <v>0.22</v>
       </c>
       <c r="H2" t="n">
-        <v>5382</v>
+        <v>4857</v>
       </c>
     </row>
     <row r="3">
@@ -528,7 +528,7 @@
         <v>0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>5190</v>
+        <v>4498</v>
       </c>
     </row>
     <row r="4">
@@ -606,7 +606,7 @@
         <v>0.21</v>
       </c>
       <c r="H6" t="n">
-        <v>1653</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="7">
@@ -658,7 +658,7 @@
         <v>0.19</v>
       </c>
       <c r="H8" t="n">
-        <v>638</v>
+        <v>563</v>
       </c>
     </row>
     <row r="9">
@@ -736,7 +736,7 @@
         <v>0.15</v>
       </c>
       <c r="H11" t="n">
-        <v>402</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12">
@@ -840,7 +840,7 @@
         <v>0.25</v>
       </c>
       <c r="H15" t="n">
-        <v>419</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16">
@@ -1204,7 +1204,7 @@
         <v>0.158</v>
       </c>
       <c r="H29" t="n">
-        <v>16663</v>
+        <v>14972</v>
       </c>
     </row>
   </sheetData>
@@ -1267,7 +1267,7 @@
         <v>0.22</v>
       </c>
       <c r="H2" t="n">
-        <v>12164</v>
+        <v>9972</v>
       </c>
     </row>
     <row r="3">
@@ -1293,7 +1293,7 @@
         <v>0.26</v>
       </c>
       <c r="H3" t="n">
-        <v>13938</v>
+        <v>11427</v>
       </c>
     </row>
     <row r="4">
@@ -1319,7 +1319,7 @@
         <v>0.16</v>
       </c>
       <c r="H4" t="n">
-        <v>5995</v>
+        <v>4915</v>
       </c>
     </row>
     <row r="5">
@@ -1345,7 +1345,7 @@
         <v>0.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3723</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="6">
@@ -1371,7 +1371,7 @@
         <v>0.28</v>
       </c>
       <c r="H6" t="n">
-        <v>3322</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="7">
@@ -1397,7 +1397,7 @@
         <v>0.095</v>
       </c>
       <c r="H7" t="n">
-        <v>688</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -1423,7 +1423,7 @@
         <v>0.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1375</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="9">
@@ -1449,7 +1449,7 @@
         <v>0.14</v>
       </c>
       <c r="H9" t="n">
-        <v>726</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10">
@@ -1475,7 +1475,7 @@
         <v>0.091</v>
       </c>
       <c r="H10" t="n">
-        <v>535</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11">
@@ -1501,7 +1501,7 @@
         <v>0.16</v>
       </c>
       <c r="H11" t="n">
-        <v>916</v>
+        <v>751</v>
       </c>
     </row>
     <row r="12">
@@ -1527,7 +1527,7 @@
         <v>0.12</v>
       </c>
       <c r="H12" t="n">
-        <v>1031</v>
+        <v>845</v>
       </c>
     </row>
     <row r="13">
@@ -1553,7 +1553,7 @@
         <v>0.15</v>
       </c>
       <c r="H13" t="n">
-        <v>1223</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="14">
@@ -1579,7 +1579,7 @@
         <v>0.13</v>
       </c>
       <c r="H14" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1605,7 +1605,7 @@
         <v>0.13</v>
       </c>
       <c r="H15" t="n">
-        <v>744</v>
+        <v>610</v>
       </c>
     </row>
     <row r="16">
@@ -1631,7 +1631,7 @@
         <v>0.79</v>
       </c>
       <c r="H16" t="n">
-        <v>860</v>
+        <v>705</v>
       </c>
     </row>
     <row r="17">
@@ -1657,7 +1657,7 @@
         <v>0.086</v>
       </c>
       <c r="H17" t="n">
-        <v>172</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18">
@@ -1683,7 +1683,7 @@
         <v>0.049</v>
       </c>
       <c r="H18" t="n">
-        <v>229</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19">
@@ -1709,7 +1709,7 @@
         <v>0.053</v>
       </c>
       <c r="H19" t="n">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20">
@@ -1735,7 +1735,7 @@
         <v>0.12</v>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -1761,7 +1761,7 @@
         <v>0.053</v>
       </c>
       <c r="H21" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
@@ -1787,7 +1787,7 @@
         <v>0.053</v>
       </c>
       <c r="H22" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -1813,7 +1813,7 @@
         <v>0.1</v>
       </c>
       <c r="H23" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -1865,7 +1865,7 @@
         <v>0.029</v>
       </c>
       <c r="H25" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -1969,7 +1969,7 @@
         <v>0.1791</v>
       </c>
       <c r="H29" t="n">
-        <v>48313</v>
+        <v>39608</v>
       </c>
     </row>
   </sheetData>
@@ -2032,7 +2032,7 @@
         <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>7556</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="3">
@@ -2058,7 +2058,7 @@
         <v>0.24</v>
       </c>
       <c r="H3" t="n">
-        <v>12109</v>
+        <v>9907</v>
       </c>
     </row>
     <row r="4">
@@ -2084,7 +2084,7 @@
         <v>0.13</v>
       </c>
       <c r="H4" t="n">
-        <v>2321</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="5">
@@ -2110,7 +2110,7 @@
         <v>0.14</v>
       </c>
       <c r="H5" t="n">
-        <v>2275</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="6">
@@ -2136,7 +2136,7 @@
         <v>0.19</v>
       </c>
       <c r="H6" t="n">
-        <v>1177</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -2162,7 +2162,7 @@
         <v>0.088</v>
       </c>
       <c r="H7" t="n">
-        <v>402</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8">
@@ -2188,7 +2188,7 @@
         <v>0.12</v>
       </c>
       <c r="H8" t="n">
-        <v>713</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9">
@@ -2214,7 +2214,7 @@
         <v>0.14</v>
       </c>
       <c r="H9" t="n">
-        <v>1141</v>
+        <v>934</v>
       </c>
     </row>
     <row r="10">
@@ -2240,7 +2240,7 @@
         <v>0.079</v>
       </c>
       <c r="H10" t="n">
-        <v>366</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
@@ -2266,7 +2266,7 @@
         <v>0.14</v>
       </c>
       <c r="H11" t="n">
-        <v>630</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12">
@@ -2292,7 +2292,7 @@
         <v>0.11</v>
       </c>
       <c r="H12" t="n">
-        <v>719</v>
+        <v>597</v>
       </c>
     </row>
     <row r="13">
@@ -2318,7 +2318,7 @@
         <v>0.065</v>
       </c>
       <c r="H13" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -2344,7 +2344,7 @@
         <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -2370,7 +2370,7 @@
         <v>0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16">
@@ -2396,7 +2396,7 @@
         <v>0.055</v>
       </c>
       <c r="H16" t="n">
-        <v>166</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
@@ -2422,7 +2422,7 @@
         <v>0.035</v>
       </c>
       <c r="H17" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18">
@@ -2448,7 +2448,7 @@
         <v>0.1503</v>
       </c>
       <c r="H18" t="n">
-        <v>29964</v>
+        <v>24909</v>
       </c>
     </row>
   </sheetData>
@@ -2511,7 +2511,7 @@
         <v>0.22</v>
       </c>
       <c r="H2" t="n">
-        <v>12164</v>
+        <v>9972</v>
       </c>
     </row>
     <row r="3">
@@ -2537,7 +2537,7 @@
         <v>0.26</v>
       </c>
       <c r="H3" t="n">
-        <v>13938</v>
+        <v>11427</v>
       </c>
     </row>
     <row r="4">
@@ -2563,7 +2563,7 @@
         <v>0.16</v>
       </c>
       <c r="H4" t="n">
-        <v>5995</v>
+        <v>4915</v>
       </c>
     </row>
     <row r="5">
@@ -2589,7 +2589,7 @@
         <v>0.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3723</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="6">
@@ -2615,7 +2615,7 @@
         <v>0.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3322</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="7">
@@ -2641,7 +2641,7 @@
         <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1375</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="8">
@@ -2667,7 +2667,7 @@
         <v>0.086</v>
       </c>
       <c r="H8" t="n">
-        <v>688</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9">
@@ -2693,7 +2693,7 @@
         <v>0.13</v>
       </c>
       <c r="H9" t="n">
-        <v>726</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10">
@@ -2719,7 +2719,7 @@
         <v>0.16</v>
       </c>
       <c r="H10" t="n">
-        <v>916</v>
+        <v>751</v>
       </c>
     </row>
     <row r="11">
@@ -2745,7 +2745,7 @@
         <v>0.11</v>
       </c>
       <c r="H11" t="n">
-        <v>1031</v>
+        <v>845</v>
       </c>
     </row>
     <row r="12">
@@ -2771,7 +2771,7 @@
         <v>0.072</v>
       </c>
       <c r="H12" t="n">
-        <v>535</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13">
@@ -2797,7 +2797,7 @@
         <v>0.15</v>
       </c>
       <c r="H13" t="n">
-        <v>1223</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="14">
@@ -2823,7 +2823,7 @@
         <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -2849,7 +2849,7 @@
         <v>0.08</v>
       </c>
       <c r="H15" t="n">
-        <v>172</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
@@ -2875,7 +2875,7 @@
         <v>0.054</v>
       </c>
       <c r="H16" t="n">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17">
@@ -2901,7 +2901,7 @@
         <v>0.04</v>
       </c>
       <c r="H17" t="n">
-        <v>229</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18">
@@ -2927,7 +2927,7 @@
         <v>0.1692</v>
       </c>
       <c r="H18" t="n">
-        <v>46438</v>
+        <v>38071</v>
       </c>
     </row>
   </sheetData>
@@ -2990,7 +2990,7 @@
         <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>7556</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="3">
@@ -3016,7 +3016,7 @@
         <v>0.24</v>
       </c>
       <c r="H3" t="n">
-        <v>12109</v>
+        <v>9907</v>
       </c>
     </row>
     <row r="4">
@@ -3042,7 +3042,7 @@
         <v>0.13</v>
       </c>
       <c r="H4" t="n">
-        <v>2321</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="5">
@@ -3068,7 +3068,7 @@
         <v>0.14</v>
       </c>
       <c r="H5" t="n">
-        <v>2275</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="6">
@@ -3094,7 +3094,7 @@
         <v>0.19</v>
       </c>
       <c r="H6" t="n">
-        <v>1177</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -3120,7 +3120,7 @@
         <v>0.088</v>
       </c>
       <c r="H7" t="n">
-        <v>402</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8">
@@ -3146,7 +3146,7 @@
         <v>0.12</v>
       </c>
       <c r="H8" t="n">
-        <v>713</v>
+        <v>581</v>
       </c>
     </row>
     <row r="9">
@@ -3172,7 +3172,7 @@
         <v>0.14</v>
       </c>
       <c r="H9" t="n">
-        <v>1141</v>
+        <v>934</v>
       </c>
     </row>
     <row r="10">
@@ -3198,7 +3198,7 @@
         <v>0.079</v>
       </c>
       <c r="H10" t="n">
-        <v>366</v>
+        <v>323</v>
       </c>
     </row>
     <row r="11">
@@ -3224,7 +3224,7 @@
         <v>0.14</v>
       </c>
       <c r="H11" t="n">
-        <v>630</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12">
@@ -3250,7 +3250,7 @@
         <v>0.11</v>
       </c>
       <c r="H12" t="n">
-        <v>719</v>
+        <v>597</v>
       </c>
     </row>
     <row r="13">
@@ -3276,7 +3276,7 @@
         <v>0.065</v>
       </c>
       <c r="H13" t="n">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -3302,7 +3302,7 @@
         <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -3328,7 +3328,7 @@
         <v>0.25</v>
       </c>
       <c r="H15" t="n">
-        <v>419</v>
+        <v>343</v>
       </c>
     </row>
     <row r="16">
@@ -3354,7 +3354,7 @@
         <v>0.1</v>
       </c>
       <c r="H16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -3380,7 +3380,7 @@
         <v>0.055</v>
       </c>
       <c r="H17" t="n">
-        <v>166</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18">
@@ -3406,7 +3406,7 @@
         <v>0.035</v>
       </c>
       <c r="H18" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -3692,7 +3692,7 @@
         <v>0.154</v>
       </c>
       <c r="H29" t="n">
-        <v>30525</v>
+        <v>25394</v>
       </c>
     </row>
   </sheetData>
@@ -3755,7 +3755,7 @@
         <v>0.22</v>
       </c>
       <c r="H2" t="n">
-        <v>12164</v>
+        <v>9972</v>
       </c>
     </row>
     <row r="3">
@@ -3781,7 +3781,7 @@
         <v>0.26</v>
       </c>
       <c r="H3" t="n">
-        <v>13938</v>
+        <v>11427</v>
       </c>
     </row>
     <row r="4">
@@ -3807,7 +3807,7 @@
         <v>0.16</v>
       </c>
       <c r="H4" t="n">
-        <v>5995</v>
+        <v>4915</v>
       </c>
     </row>
     <row r="5">
@@ -3833,7 +3833,7 @@
         <v>0.16</v>
       </c>
       <c r="H5" t="n">
-        <v>3723</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="6">
@@ -3859,7 +3859,7 @@
         <v>0.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3322</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="7">
@@ -3885,7 +3885,7 @@
         <v>0.2</v>
       </c>
       <c r="H7" t="n">
-        <v>1375</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="8">
@@ -3911,7 +3911,7 @@
         <v>0.086</v>
       </c>
       <c r="H8" t="n">
-        <v>688</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9">
@@ -3937,7 +3937,7 @@
         <v>0.13</v>
       </c>
       <c r="H9" t="n">
-        <v>726</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10">
@@ -3963,7 +3963,7 @@
         <v>0.16</v>
       </c>
       <c r="H10" t="n">
-        <v>916</v>
+        <v>751</v>
       </c>
     </row>
     <row r="11">
@@ -3989,7 +3989,7 @@
         <v>0.11</v>
       </c>
       <c r="H11" t="n">
-        <v>1031</v>
+        <v>845</v>
       </c>
     </row>
     <row r="12">
@@ -4015,7 +4015,7 @@
         <v>0.072</v>
       </c>
       <c r="H12" t="n">
-        <v>535</v>
+        <v>439</v>
       </c>
     </row>
     <row r="13">
@@ -4041,7 +4041,7 @@
         <v>0.15</v>
       </c>
       <c r="H13" t="n">
-        <v>1223</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="14">
@@ -4067,7 +4067,7 @@
         <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>114</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -4093,7 +4093,7 @@
         <v>0.13</v>
       </c>
       <c r="H15" t="n">
-        <v>744</v>
+        <v>610</v>
       </c>
     </row>
     <row r="16">
@@ -4119,7 +4119,7 @@
         <v>0.79</v>
       </c>
       <c r="H16" t="n">
-        <v>860</v>
+        <v>705</v>
       </c>
     </row>
     <row r="17">
@@ -4145,7 +4145,7 @@
         <v>0.08</v>
       </c>
       <c r="H17" t="n">
-        <v>172</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18">
@@ -4171,7 +4171,7 @@
         <v>0.054</v>
       </c>
       <c r="H18" t="n">
-        <v>287</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19">
@@ -4197,7 +4197,7 @@
         <v>0.04</v>
       </c>
       <c r="H19" t="n">
-        <v>229</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20">
@@ -4223,7 +4223,7 @@
         <v>0.12</v>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -4249,7 +4249,7 @@
         <v>0.053</v>
       </c>
       <c r="H21" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22">
@@ -4275,7 +4275,7 @@
         <v>0.053</v>
       </c>
       <c r="H22" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -4301,7 +4301,7 @@
         <v>0.1</v>
       </c>
       <c r="H23" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24">
@@ -4353,7 +4353,7 @@
         <v>0.029</v>
       </c>
       <c r="H25" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26">
@@ -4457,7 +4457,7 @@
         <v>0.1744</v>
       </c>
       <c r="H29" t="n">
-        <v>48313</v>
+        <v>39608</v>
       </c>
     </row>
   </sheetData>
